--- a/Buoi2/BT1.xlsx
+++ b/Buoi2/BT1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\Kiem_thu_phan_mem\Buoi2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B406317-0280-495D-A8CB-DE3C3F63228A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9626254-064F-4DE9-8D38-F2B4769407B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1950" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{4DCF6CBE-5135-4433-8EE3-D3D0176D38E0}"/>
+    <workbookView xWindow="28680" yWindow="-1950" windowWidth="29040" windowHeight="17520" activeTab="6" xr2:uid="{4DCF6CBE-5135-4433-8EE3-D3D0176D38E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Bài 1" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="275">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -242,6 +242,9 @@
     <t>Hệ thống báo lỗi độ dài</t>
   </si>
   <si>
+    <t>TG02</t>
+  </si>
+  <si>
     <t>Kiểm tra độ dài biên dưới hợp lệ ($L = 6$)</t>
   </si>
   <si>
@@ -251,6 +254,9 @@
     <t>Kiểm tra độ dài nằm giữa khoảng hợp lệ</t>
   </si>
   <si>
+    <t>TG03</t>
+  </si>
+  <si>
     <t>Kiểm tra độ dài biên trên hợp lệ ($L = 10$)</t>
   </si>
   <si>
@@ -393,6 +399,477 @@
   </si>
   <si>
     <t>Tính giá Bình thường</t>
+  </si>
+  <si>
+    <t>TC_TICKET_04</t>
+  </si>
+  <si>
+    <t>Kiểm thử giá vé theo chiều cao (cm)</t>
+  </si>
+  <si>
+    <t>Truy cập website bán vé</t>
+  </si>
+  <si>
+    <t>-10 (Âm - Invalid)</t>
+  </si>
+  <si>
+    <t>50 (40-99 - Miễn phí)</t>
+  </si>
+  <si>
+    <t>120 (100-140 - 150k)</t>
+  </si>
+  <si>
+    <t>160 (141-200 - 300k)</t>
+  </si>
+  <si>
+    <t>210 (Trên 200 - Error)</t>
+  </si>
+  <si>
+    <t>Phân vùng chiều cao (Height h)</t>
+  </si>
+  <si>
+    <t>Kết quả / Giá vé</t>
+  </si>
+  <si>
+    <t>Vùng không hợp lệ</t>
+  </si>
+  <si>
+    <t>Vùng không xác định/Invalid</t>
+  </si>
+  <si>
+    <t>Vùng hợp lệ 1</t>
+  </si>
+  <si>
+    <t>Vùng hợp lệ 2</t>
+  </si>
+  <si>
+    <t>Vùng hợp lệ 3</t>
+  </si>
+  <si>
+    <t>Vùng lỗi (Invalid)</t>
+  </si>
+  <si>
+    <t>Không được chấp nhận (Do quy định bắt đầu từ 40)</t>
+  </si>
+  <si>
+    <t>h &lt; 0 hoặc nhập chữ</t>
+  </si>
+  <si>
+    <t>0 &lt;= h &lt; 40</t>
+  </si>
+  <si>
+    <t>100 &lt;= h &lt;= 140</t>
+  </si>
+  <si>
+    <t>40 &lt;= h &lt;= 99</t>
+  </si>
+  <si>
+    <t>141 &lt;= h &lt;= 200</t>
+  </si>
+  <si>
+    <t>h &gt; 200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Báo lỗi định dạng/số âm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miễn phí </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông báo lỗi </t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập số âm</t>
+  </si>
+  <si>
+    <t>Hệ thống báo lỗi số âm</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập chiều cao quá thấp (Chưa đủ tuổi/chiều cao)</t>
+  </si>
+  <si>
+    <t>Không chấp nhận / Báo lỗi</t>
+  </si>
+  <si>
+    <t>Kiểm tra vùng miễn phí ($40 \le h \le 99$)</t>
+  </si>
+  <si>
+    <t>Kiểm tra biên chuyển giá vé 1 ($h=100$)</t>
+  </si>
+  <si>
+    <t>Kiểm tra vùng giá vé trung bình ($100 \le h \le 140$)</t>
+  </si>
+  <si>
+    <t>Kiểm tra vùng giá vé cao ($141 \le h \le 200$)</t>
+  </si>
+  <si>
+    <t>Kiểm tra chiều cao vượt quá giới hạn ($h &gt; 200$)</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo lỗi</t>
+  </si>
+  <si>
+    <t>TC08</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập ký tự chữ</t>
+  </si>
+  <si>
+    <t>"abc"</t>
+  </si>
+  <si>
+    <t>Hệ thống báo lỗi định dạng</t>
+  </si>
+  <si>
+    <t>Giá vé: Miễn phí</t>
+  </si>
+  <si>
+    <t>Giá vé: 150,000</t>
+  </si>
+  <si>
+    <t>Giá vé: 300,000</t>
+  </si>
+  <si>
+    <t>TC_SALE_05</t>
+  </si>
+  <si>
+    <t>Kiểm thử mã giảm giá theo ngày nhập (20-30)</t>
+  </si>
+  <si>
+    <t>Truy cập website sự kiện sale</t>
+  </si>
+  <si>
+    <t>Ngày = 15 (Invalid)</t>
+  </si>
+  <si>
+    <t>Ngày = 22 (Valid 50%)</t>
+  </si>
+  <si>
+    <t>Ngày = 28 (Valid 70%)</t>
+  </si>
+  <si>
+    <t>Ngày = 35 (Invalid)</t>
+  </si>
+  <si>
+    <t>Phân vùng ngày nhập (Day d)</t>
+  </si>
+  <si>
+    <t>Kết quả / Coupon</t>
+  </si>
+  <si>
+    <t>Vùng hợp lệ 1 (Valid)</t>
+  </si>
+  <si>
+    <t>Vùng hợp lệ 2 (Valid)</t>
+  </si>
+  <si>
+    <t>Vùng sai định dạng (Invalid)</t>
+  </si>
+  <si>
+    <t>Ký tự chữ, số thập phân</t>
+  </si>
+  <si>
+    <t>Hệ thống tự động báo lỗi</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập ký tự không phải số nguyên</t>
+  </si>
+  <si>
+    <t>"25a"</t>
+  </si>
+  <si>
+    <t>Nhận được mã giảm giá 50%</t>
+  </si>
+  <si>
+    <t>Nhận được mã giảm giá 70%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Báo lỗi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giảm giá 50% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giảm giá 70% </t>
+  </si>
+  <si>
+    <t>d &lt; 20</t>
+  </si>
+  <si>
+    <t>d &gt; 30</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập ngày nhỏ hơn khoảng cho phép (d &lt; 20)</t>
+  </si>
+  <si>
+    <t>Kiểm tra biên dưới của vùng 70% (d=26)</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập ngày lớn hơn khoảng cho phép (d &gt; 30)</t>
+  </si>
+  <si>
+    <t>20 &lt;= d &lt;= 25</t>
+  </si>
+  <si>
+    <t>26 &lt;= d &lt;= 30</t>
+  </si>
+  <si>
+    <t>Kiểm tra vùng giảm giá 50% (20 &lt;= d &lt;= 25)</t>
+  </si>
+  <si>
+    <t>Kiểm tra vùng giảm giá 70% (26 &lt;= d &lt;= 30)</t>
+  </si>
+  <si>
+    <t>TC_INT_06</t>
+  </si>
+  <si>
+    <t>Kiểm thử ô nhập số nguyên theo độ dài ký tự [1-10] hoặc [20-30]</t>
+  </si>
+  <si>
+    <t>Mở form có ô nhập liệu</t>
+  </si>
+  <si>
+    <t>Rỗng (Length = 0, Invalid)</t>
+  </si>
+  <si>
+    <t>"12345" (Length = 5, Valid)</t>
+  </si>
+  <si>
+    <t>Phân vùng độ dài ký tự (Length L)</t>
+  </si>
+  <si>
+    <t>Kết quả</t>
+  </si>
+  <si>
+    <t>L &gt; 30</t>
+  </si>
+  <si>
+    <t>Vùng sai định dạng</t>
+  </si>
+  <si>
+    <t>Ký tự không phải số nguyên</t>
+  </si>
+  <si>
+    <t>L &lt; 1 (Rỗng)</t>
+  </si>
+  <si>
+    <t>10 &lt; L &lt; 20 (Khoảng giữa)</t>
+  </si>
+  <si>
+    <t>Kiểm tra độ dài nhỏ hơn 1 (Rỗng)</t>
+  </si>
+  <si>
+    <t>Hệ thống yêu cầu nhập dữ liệu</t>
+  </si>
+  <si>
+    <t>25 chữ số "1"</t>
+  </si>
+  <si>
+    <t>35 chữ số "1"</t>
+  </si>
+  <si>
+    <t>Hệ thống báo lỗi độ dài quá lớn</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập ký tự chữ cái (Sai định dạng)</t>
+  </si>
+  <si>
+    <t>"abcde"</t>
+  </si>
+  <si>
+    <t>Hệ thống báo lỗi phải là số nguyên</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhập ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>"@#$%"</t>
+  </si>
+  <si>
+    <t>"" (Không nhập gì)</t>
+  </si>
+  <si>
+    <t>"123456789012345" (15 ký tự)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chấp nhận </t>
+  </si>
+  <si>
+    <t>1 &lt;= L &lt;= 10</t>
+  </si>
+  <si>
+    <t>20 &lt;= L &lt;= 30</t>
+  </si>
+  <si>
+    <t>Kiểm tra độ dài thuộc vùng hợp lệ 1 (1 &lt;= L &lt;= 10)</t>
+  </si>
+  <si>
+    <t>Kiểm tra độ dài thuộc vùng "lửng" không hợp lệ (10 &lt; L &lt; 20)</t>
+  </si>
+  <si>
+    <t>Kiểm tra độ dài thuộc vùng hợp lệ 2 (20 &lt;= L &lt;= 30)</t>
+  </si>
+  <si>
+    <t>Kiểm tra độ dài lớn hơn giới hạn cho phép (L &gt; 30)</t>
+  </si>
+  <si>
+    <t>"123456789101112" (Length = 15, Invalid)</t>
+  </si>
+  <si>
+    <t>"1234567891011121314151617" (Length = 25, Valid)</t>
+  </si>
+  <si>
+    <t>"12345678910111213141516171819202122" (Length = 35, Invalid)</t>
+  </si>
+  <si>
+    <t>TC_STATS_07</t>
+  </si>
+  <si>
+    <t>Kiểm thử xử lý file điểm sinh viên (Max 100 dòng, tên, điểm)</t>
+  </si>
+  <si>
+    <t>Có file dữ liệu đầu vào (.txt/csv)</t>
+  </si>
+  <si>
+    <t>File chuẩn (5 SV, điểm hợp lệ)</t>
+  </si>
+  <si>
+    <t>File quá lớn (101 dòng - Invalid)</t>
+  </si>
+  <si>
+    <t>Tên dài &gt; 20 ký tự (Invalid)</t>
+  </si>
+  <si>
+    <t>Điểm = -1 hoặc 11 (Invalid)</t>
+  </si>
+  <si>
+    <t>Giới tính sai (2 ký tự - Invalid)</t>
+  </si>
+  <si>
+    <t>Tiêu chí</t>
+  </si>
+  <si>
+    <t>Vùng Hợp lệ (Valid)</t>
+  </si>
+  <si>
+    <t>Vùng Không hợp lệ (Invalid)</t>
+  </si>
+  <si>
+    <t>Số lượng dòng (N)</t>
+  </si>
+  <si>
+    <t>Độ dài Tên (L)</t>
+  </si>
+  <si>
+    <t>Giới tính (G)</t>
+  </si>
+  <si>
+    <t>1 ký tự (Ví dụ: 'M', 'F')</t>
+  </si>
+  <si>
+    <t>Điểm số (S)</t>
+  </si>
+  <si>
+    <t>Bộ dữ liệu (Input Data - Nội dung File)</t>
+  </si>
+  <si>
+    <t>Kiểm tra file hợp lệ (Tính toán đúng)</t>
+  </si>
+  <si>
+    <t>File chứa 3 SV:</t>
+  </si>
+  <si>
+    <t>1. Nguyen Van A, M, 8,8,8,8,8</t>
+  </si>
+  <si>
+    <t>2. Tran Thi B, F, 4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>3. Le Van C, M, 6,6,6,6,6</t>
+  </si>
+  <si>
+    <t>- Đọc thành công.</t>
+  </si>
+  <si>
+    <t>- TB mỗi SV: A(8.0), B(4.0), C(6.0)</t>
+  </si>
+  <si>
+    <t>- Số SV lên lớp: 2 (A và C)</t>
+  </si>
+  <si>
+    <t>File chứa 101 dòng thông tin sinh viên</t>
+  </si>
+  <si>
+    <t>Hệ thống báo lỗi hoặc chỉ xử lý 100 dòng đầu</t>
+  </si>
+  <si>
+    <t>Báo lỗi dữ liệu tên tại dòng đó</t>
+  </si>
+  <si>
+    <t>Kiểm tra điểm số không hợp lệ (Điểm âm)</t>
+  </si>
+  <si>
+    <t>Báo lỗi dữ liệu điểm không hợp lệ</t>
+  </si>
+  <si>
+    <t>Kiểm tra điểm số không hợp lệ (Điểm &gt; 10)</t>
+  </si>
+  <si>
+    <t>Kiểm tra định dạng giới tính sai (&gt; 1 ký tự)</t>
+  </si>
+  <si>
+    <t>Báo lỗi định dạng giới tính (chỉ nhận 1 ký tự)</t>
+  </si>
+  <si>
+    <t>- TB: 2.8</t>
+  </si>
+  <si>
+    <t>- Không tính vào danh sách "Lên lớp"</t>
+  </si>
+  <si>
+    <t>1 dòng: "Nguyen Tran Le Hoang Vu Long Lanh", M, 8,8,8,8,8</t>
+  </si>
+  <si>
+    <t>1 dòng: Le Van D, M, -1, 5, 5, 5, 5</t>
+  </si>
+  <si>
+    <t>1 dòng: Le Van E, M, 11, 5, 5, 5, 5</t>
+  </si>
+  <si>
+    <t>1 dòng: Le Van F, Male, 7, 7, 7, 7, 7</t>
+  </si>
+  <si>
+    <t>1 dòng: Student Fail, F, 2, 2, 3, 3, 4</t>
+  </si>
+  <si>
+    <t>Kiểm tra số lượng dòng vượt quá giới hạn (N &gt; 100)</t>
+  </si>
+  <si>
+    <t>Kiểm tra độ dài tên quá dài (L &gt; 20)</t>
+  </si>
+  <si>
+    <t>N = 0 (File rỗng) hoặc N &gt; 100</t>
+  </si>
+  <si>
+    <t>L = 0 hoặc L &gt; 20 ký tự</t>
+  </si>
+  <si>
+    <t>0 ký tự hoặc &gt; 1 ký tự</t>
+  </si>
+  <si>
+    <t>S &lt; 0 hoặc S &gt; 10 hoặc Ký tự chữ</t>
+  </si>
+  <si>
+    <t>Kiểm tra logic sinh viên rớt (TB &lt;= 5)</t>
+  </si>
+  <si>
+    <t>1 &lt;= N &lt;= 100 dòng</t>
+  </si>
+  <si>
+    <t>1 &lt;= L &lt;= 20 ký tự</t>
+  </si>
+  <si>
+    <t>0 &lt;= S &lt;= 10</t>
   </si>
 </sst>
 </file>
@@ -447,7 +924,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -477,6 +954,15 @@
       <alignment vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="46" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1268,7 +1754,7 @@
         <v>6</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1296,7 +1782,7 @@
         <v>57</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E17" s="1"/>
     </row>
@@ -1351,7 +1837,7 @@
         <v>63</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>64</v>
@@ -1365,13 +1851,13 @@
         <v>27</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>10</v>
@@ -1382,13 +1868,13 @@
         <v>28</v>
       </c>
       <c r="B27" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>10</v>
@@ -1399,13 +1885,13 @@
         <v>45</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>10</v>
@@ -1413,13 +1899,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>64</v>
@@ -1433,13 +1919,13 @@
         <v>45</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>10</v>
@@ -1469,13 +1955,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
@@ -1565,14 +2051,14 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F8" s="7"/>
     </row>
@@ -1584,7 +2070,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F9" s="7"/>
     </row>
@@ -1596,7 +2082,7 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F10" s="7"/>
     </row>
@@ -1608,7 +2094,7 @@
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F11" s="7"/>
     </row>
@@ -1620,7 +2106,7 @@
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F12" s="7"/>
     </row>
@@ -1645,10 +2131,10 @@
       <c r="B15" s="7"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F15" s="7"/>
     </row>
@@ -1656,13 +2142,13 @@
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F16" s="7"/>
     </row>
@@ -1670,13 +2156,13 @@
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F17" s="7"/>
     </row>
@@ -1684,13 +2170,13 @@
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F18" s="7"/>
     </row>
@@ -1698,13 +2184,13 @@
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F19" s="7"/>
     </row>
@@ -1712,13 +2198,13 @@
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F20" s="7"/>
     </row>
@@ -1769,13 +2255,13 @@
         <v>25</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C25" s="9">
         <v>0.34375</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>10</v>
@@ -1787,13 +2273,13 @@
         <v>27</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C26" s="9">
         <v>0.39583333333333331</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>10</v>
@@ -1805,13 +2291,13 @@
         <v>28</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C27" s="9">
         <v>0.54166666666666663</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>10</v>
@@ -1823,13 +2309,13 @@
         <v>45</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C28" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>10</v>
@@ -1838,16 +2324,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C29" s="9">
         <v>0.72916666666666663</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>10</v>
@@ -1856,16 +2342,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C30" s="9">
         <v>0.875</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>10</v>
@@ -1874,16 +2360,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C31" s="10">
         <v>1.0416666666666667</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>10</v>
@@ -1897,36 +2383,1873 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC1D454A-9FC7-46FB-A19E-37345831C2F5}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5">
+        <v>46174</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3">
+        <v>4</v>
+      </c>
+      <c r="E11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E19" s="11">
+        <v>150000</v>
+      </c>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" s="11">
+        <v>300000</v>
+      </c>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C25" s="3">
+        <v>-10</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" s="3">
+        <v>30</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" s="3">
+        <v>50</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" s="3">
+        <v>100</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="3">
+        <v>120</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C30" s="3">
+        <v>160</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C31" s="3">
+        <v>210</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE63B7F1-48A6-48D4-9C68-BC2116108814}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5">
+        <v>46174</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3">
+        <v>4</v>
+      </c>
+      <c r="E11" t="s">
+        <v>167</v>
+      </c>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C25" s="3">
+        <v>15</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" s="3">
+        <v>22</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="3">
+        <v>26</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" s="3">
+        <v>29</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="3">
+        <v>31</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7792ED-3732-4922-9A6B-78771CF0673C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5">
+        <v>46174</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>194</v>
+      </c>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>195</v>
+      </c>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>222</v>
+      </c>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3">
+        <v>4</v>
+      </c>
+      <c r="E11" t="s">
+        <v>223</v>
+      </c>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>224</v>
+      </c>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5607F8-6129-499C-975B-6751906C3F9C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5">
+        <v>46174</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>228</v>
+      </c>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>229</v>
+      </c>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>230</v>
+      </c>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3">
+        <v>4</v>
+      </c>
+      <c r="E11" t="s">
+        <v>231</v>
+      </c>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>232</v>
+      </c>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E27" s="12"/>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E29" s="12"/>
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D31" s="13"/>
+      <c r="E31" s="12"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="12"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="12"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="12"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E39" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="B25:B31"/>
+    <mergeCell ref="E25:E31"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="E37:E39"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Buoi2/BT1.xlsx
+++ b/Buoi2/BT1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\Kiem_thu_phan_mem\Buoi2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9626254-064F-4DE9-8D38-F2B4769407B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A877005F-ECDA-4B26-B2E5-EC0CEC4108B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1950" windowWidth="29040" windowHeight="17520" activeTab="6" xr2:uid="{4DCF6CBE-5135-4433-8EE3-D3D0176D38E0}"/>
+    <workbookView xWindow="28680" yWindow="-1950" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{4DCF6CBE-5135-4433-8EE3-D3D0176D38E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Bài 1" sheetId="7" r:id="rId1"/>
